--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2314" uniqueCount="412">
   <si>
     <t>Property</t>
   </si>
@@ -120,7 +120,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Communication</t>
+    <t>https://gematik.de/fhir/tiflow-erezept/StructureDefinition/GEM-ERP-PR-Communication</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -499,6 +499,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Communication.meta.tag</t>
   </si>
   <si>
@@ -640,10 +647,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Communication.modifierExtension</t>
   </si>
   <si>
@@ -685,6 +688,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -698,6 +704,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -726,308 +735,39 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_PR_Task) &lt;&lt;referenced&gt;&gt;
 </t>
   </si>
   <si>
-    <t>Request fulfilled by this communication</t>
+    <t>Gibt das E-Rezept-Token gemäß gemSpec_DM_eRp an.</t>
   </si>
   <si>
     <t>An order, proposal or plan fulfilled in whole or in part by this Communication.</t>
   </si>
   <si>
-    <t>This must point to some sort of a 'Request' resource, such as CarePlan, CommunicationRequest, ServiceRequest, MedicationRequest, etc.</t>
+    <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
   </si>
   <si>
-    <t>Communication.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">container
-</t>
-  </si>
-  <si>
-    <t>Part of this action</t>
-  </si>
-  <si>
-    <t>Part of this action.</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>Communication.inResponseTo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Communication|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Reply to</t>
-  </si>
-  <si>
-    <t>Prior communication that this communication is in response to.</t>
-  </si>
-  <si>
-    <t>Communication.status</t>
-  </si>
-  <si>
-    <t>preparation | in-progress | not-done | on-hold | stopped | completed | entered-in-error | unknown</t>
-  </si>
-  <si>
-    <t>The status of the transmission.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains the codes aborted and entered-in-error that mark the communication as not currently valid.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>The status of the communication.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/event-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Communication.statusReason</t>
-  </si>
-  <si>
-    <t>Suspended Reason
-Cancelled Reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Reason for current status</t>
-  </si>
-  <si>
-    <t>Captures the reason for the current state of the Communication.</t>
-  </si>
-  <si>
-    <t>This is generally only used for "exception" statuses such as "not-done", "suspended" or "aborted". The reason for performing the event at all is captured in reasonCode, not here.</t>
-  </si>
-  <si>
-    <t>Codes for the reason why a communication did not happen.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-not-done-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.statusReason</t>
-  </si>
-  <si>
-    <t>Communication.category</t>
-  </si>
-  <si>
-    <t>Message category</t>
-  </si>
-  <si>
-    <t>The type of message conveyed such as alert, notification, reminder, instruction, etc.</t>
-  </si>
-  <si>
-    <t>There may be multiple axes of categorization and one communication may serve multiple purposes.</t>
-  </si>
-  <si>
-    <t>Codes for general categories of communications such as alerts, instructions, etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-category|4.0.1</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Communication.priority</t>
-  </si>
-  <si>
-    <t>routine | urgent | asap | stat</t>
-  </si>
-  <si>
-    <t>Characterizes how quickly the planned or in progress communication must be addressed. Includes concepts such as stat, urgent, routine.</t>
-  </si>
-  <si>
-    <t>Used to prioritize workflow (such as which communication to read first) when the communication is planned or in progress.</t>
-  </si>
-  <si>
-    <t>If missing, this communication should be treated with normal priority</t>
-  </si>
-  <si>
-    <t>Codes indicating the relative importance of a communication.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
-  </si>
-  <si>
-    <t>FiveWs.grade</t>
-  </si>
-  <si>
-    <t>Communication.medium</t>
-  </si>
-  <si>
-    <t>A channel of communication</t>
-  </si>
-  <si>
-    <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ParticipationMode</t>
-  </si>
-  <si>
-    <t>Communication.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Focus of message</t>
-  </si>
-  <si>
-    <t>The patient or group that was the focus of this communication.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Communication.topic</t>
-  </si>
-  <si>
-    <t>Description of the purpose/content</t>
-  </si>
-  <si>
-    <t>Description of the purpose/content, similar to a subject line in an email.</t>
-  </si>
-  <si>
-    <t>Communication.topic.text can be used without any codings.</t>
-  </si>
-  <si>
-    <t>Codes describing the purpose or content of the communication.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-topic|4.0.1</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Communication.about</t>
-  </si>
-  <si>
-    <t>Resources that pertain to this communication</t>
-  </si>
-  <si>
-    <t>Other resources that pertain to this communication and to which this communication should be associated.</t>
-  </si>
-  <si>
-    <t>Don't use Communication.about element when a more specific element exists, such as basedOn or reasonReference.</t>
-  </si>
-  <si>
-    <t>Communication.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Encounter created as part of</t>
-  </si>
-  <si>
-    <t>The Encounter during which this Communication was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>Communication.sent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>When sent</t>
-  </si>
-  <si>
-    <t>The time when this communication was sent.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x] {Invariant: maps to period.start}</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Communication.received</t>
-  </si>
-  <si>
-    <t>When received</t>
-  </si>
-  <si>
-    <t>The time when this communication arrived at the destination.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x] {Invariant: maps to period.end}</t>
-  </si>
-  <si>
-    <t>Communication.recipient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Group|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Message recipient</t>
-  </si>
-  <si>
-    <t>The entity (e.g. person, organization, clinical information system, care team or device) which was the target of the communication. If receipts need to be tracked by an individual, a separate resource instance will need to be created for each recipient.  Multiple recipient communications are intended where either receipts are not tracked (e.g. a mass mail-out) or a receipt is captured in aggregate (all emails confirmed received by a particular time).</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Communication.recipient.id</t>
-  </si>
-  <si>
-    <t>Communication.recipient.extension</t>
-  </si>
-  <si>
-    <t>Communication.recipient.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
+    <t>Communication.basedOn.id</t>
+  </si>
+  <si>
+    <t>Communication.basedOn.extension</t>
+  </si>
+  <si>
+    <t>Communication.basedOn.reference</t>
   </si>
   <si>
     <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
   </si>
   <si>
     <t>Reference.reference</t>
@@ -1037,7 +777,7 @@
 </t>
   </si>
   <si>
-    <t>Communication.recipient.type</t>
+    <t>Communication.basedOn.type</t>
   </si>
   <si>
     <t>Type the reference refers to (e.g. "Patient")</t>
@@ -1059,11 +799,7 @@
     <t>Reference.type</t>
   </si>
   <si>
-    <t>Communication.recipient.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
-</t>
+    <t>Communication.basedOn.identifier</t>
   </si>
   <si>
     <t>Logical reference, when literal reference is not known</t>
@@ -1084,19 +820,339 @@
     <t>.identifier</t>
   </si>
   <si>
+    <t>Communication.basedOn.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
+    <t>Communication.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">container
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Part of this action</t>
+  </si>
+  <si>
+    <t>Part of this action.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>Event.partOf</t>
+  </si>
+  <si>
+    <t>Communication.inResponseTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Communication|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Reply to</t>
+  </si>
+  <si>
+    <t>Prior communication that this communication is in response to.</t>
+  </si>
+  <si>
+    <t>Communication.status</t>
+  </si>
+  <si>
+    <t>preparation | in-progress | not-done | on-hold | stopped | completed | entered-in-error | unknown</t>
+  </si>
+  <si>
+    <t>The status of the transmission.</t>
+  </si>
+  <si>
+    <t>Muss standardmäßig laut FHIR Core Specification angegeben werden, wird jedoch während des Lebenszyklus der Ressource nicht verändert.</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of the communication.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/event-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Communication.statusReason</t>
+  </si>
+  <si>
+    <t>Suspended Reason
+Cancelled Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Reason for current status</t>
+  </si>
+  <si>
+    <t>Captures the reason for the current state of the Communication.</t>
+  </si>
+  <si>
+    <t>This is generally only used for "exception" statuses such as "not-done", "suspended" or "aborted". The reason for performing the event at all is captured in reasonCode, not here.</t>
+  </si>
+  <si>
+    <t>Codes for the reason why a communication did not happen.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/communication-not-done-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.statusReason</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>Communication.category</t>
+  </si>
+  <si>
+    <t>Message category</t>
+  </si>
+  <si>
+    <t>The type of message conveyed such as alert, notification, reminder, instruction, etc.</t>
+  </si>
+  <si>
+    <t>There may be multiple axes of categorization and one communication may serve multiple purposes.</t>
+  </si>
+  <si>
+    <t>Codes for general categories of communications such as alerts, instructions, etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/communication-category|4.0.1</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Communication.priority</t>
+  </si>
+  <si>
+    <t>routine | urgent | asap | stat</t>
+  </si>
+  <si>
+    <t>Characterizes how quickly the planned or in progress communication must be addressed. Includes concepts such as stat, urgent, routine.</t>
+  </si>
+  <si>
+    <t>Used to prioritize workflow (such as which communication to read first) when the communication is planned or in progress.</t>
+  </si>
+  <si>
+    <t>If missing, this communication should be treated with normal priority</t>
+  </si>
+  <si>
+    <t>Codes indicating the relative importance of a communication.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+  </si>
+  <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
+    <t>Communication.medium</t>
+  </si>
+  <si>
+    <t>A channel of communication</t>
+  </si>
+  <si>
+    <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
+    <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ParticipationMode</t>
+  </si>
+  <si>
+    <t>Communication.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Focus of message</t>
+  </si>
+  <si>
+    <t>The patient or group that was the focus of this communication.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Communication.topic</t>
+  </si>
+  <si>
+    <t>Description of the purpose/content</t>
+  </si>
+  <si>
+    <t>Description of the purpose/content, similar to a subject line in an email.</t>
+  </si>
+  <si>
+    <t>Communication.topic.text can be used without any codings.</t>
+  </si>
+  <si>
+    <t>Codes describing the purpose or content of the communication.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/communication-topic|4.0.1</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Communication.about</t>
+  </si>
+  <si>
+    <t>Resources that pertain to this communication</t>
+  </si>
+  <si>
+    <t>Other resources that pertain to this communication and to which this communication should be associated.</t>
+  </si>
+  <si>
+    <t>Don't use Communication.about element when a more specific element exists, such as basedOn or reasonReference.</t>
+  </si>
+  <si>
+    <t>Communication.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Encounter created as part of</t>
+  </si>
+  <si>
+    <t>The Encounter during which this Communication was created or to which the creation of this record is tightly associated.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>Communication.sent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Der Zeitpunkt, zu dem diese Kommunikation gesendet wurde.</t>
+  </si>
+  <si>
+    <t>The time when this communication was sent.</t>
+  </si>
+  <si>
+    <t>Wird vom TIFlow-Server gesetzt. Ein Client hat diesen Wert daher immer verfügbar.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x] {Invariant: maps to period.start}</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Communication.received</t>
+  </si>
+  <si>
+    <t>Der Zeitpunkt, zu dem diese Kommunikation empfangen wurde.</t>
+  </si>
+  <si>
+    <t>The time when this communication arrived at the destination.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x] {Invariant: maps to period.end}</t>
+  </si>
+  <si>
+    <t>Communication.recipient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Group|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Die Entität (z. B. Person, Organisation), die Ziel der Kommunikation war.</t>
+  </si>
+  <si>
+    <t>The entity (e.g. person, organization, clinical information system, care team or device) which was the target of the communication. If receipts need to be tracked by an individual, a separate resource instance will need to be created for each recipient.  Multiple recipient communications are intended where either receipts are not tracked (e.g. a mass mail-out) or a receipt is captured in aggregate (all emails confirmed received by a particular time).</t>
+  </si>
+  <si>
+    <t>Muss vom Absender der Kommunikation gesetzt werden, um das Ziel festzulegen.</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Communication.recipient.id</t>
+  </si>
+  <si>
+    <t>Communication.recipient.extension</t>
+  </si>
+  <si>
+    <t>Communication.recipient.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Communication.recipient.type</t>
+  </si>
+  <si>
+    <t>Communication.recipient.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
+</t>
+  </si>
+  <si>
     <t>Communication.recipient.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>Communication.sender</t>
@@ -1106,10 +1162,14 @@
 </t>
   </si>
   <si>
-    <t>Message sender</t>
-  </si>
-  <si>
-    <t>The entity (e.g. person, organization, clinical information system, or device) which was the source of the communication.</t>
+    <t>Die Entität (z. B. Person, Organisation), die Quelle der Kommunikation war.</t>
+  </si>
+  <si>
+    <t>Nachrichtenabsender — wird vom TIFlow-Server gesetzt.
+Die Entität (z. B. Person, Organisation), die Quelle der Kommunikation war.</t>
+  </si>
+  <si>
+    <t>Wird vom TIFlow-Server gesetzt.</t>
   </si>
   <si>
     <t>Communication.sender.id</t>
@@ -1219,7 +1279,7 @@
     <t>Communication.payload.content[x]</t>
   </si>
   <si>
-    <t>Message part content</t>
+    <t>Der tatsächliche Inhalt der Nachricht</t>
   </si>
   <si>
     <t>A communicated content (or for multi-part communications, one portion of the communication).</t>
@@ -1238,7 +1298,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1559,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM59"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.87890625" customWidth="true" bestFit="true"/>
@@ -1599,7 +1665,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2270,7 +2336,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>117</v>
       </c>
@@ -2289,7 +2355,7 @@
         <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>77</v>
@@ -2381,7 +2447,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
@@ -2400,7 +2466,7 @@
         <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>77</v>
@@ -2923,7 +2989,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
@@ -2935,15 +3001,15 @@
         <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2969,13 +3035,13 @@
         <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3001,13 +3067,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3025,7 +3091,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3034,7 +3100,7 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>99</v>
@@ -3046,15 +3112,15 @@
         <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3080,13 +3146,13 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3136,7 +3202,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3162,10 +3228,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3188,16 +3254,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3223,13 +3289,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3247,7 +3313,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3273,14 +3339,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3299,16 +3365,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3358,7 +3424,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3379,19 +3445,19 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3410,16 +3476,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3469,7 +3535,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3490,15 +3556,15 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3524,10 +3590,10 @@
         <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3578,7 +3644,7 @@
         <v>114</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3604,13 +3670,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -3632,13 +3698,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3689,7 +3755,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3698,7 +3764,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -3715,10 +3781,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3744,16 +3810,16 @@
         <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3790,19 +3856,19 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3823,15 +3889,15 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3854,19 +3920,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3915,7 +3981,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3924,27 +3990,27 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3955,7 +4021,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -3967,15 +4033,17 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4024,7 +4092,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4039,21 +4107,21 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4064,7 +4132,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4079,13 +4147,13 @@
         <v>129</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4135,7 +4203,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4150,35 +4218,35 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
@@ -4187,16 +4255,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4246,7 +4314,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4255,38 +4323,38 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>234</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4295,16 +4363,16 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>101</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>235</v>
+        <v>103</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4355,40 +4423,40 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>232</v>
+        <v>104</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4407,15 +4475,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>109</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4452,19 +4522,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>115</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4476,7 +4546,7 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
@@ -4485,15 +4555,15 @@
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4507,25 +4577,25 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4551,13 +4621,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4578,37 +4648,37 @@
         <v>241</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>248</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>249</v>
+        <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4627,16 +4697,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>252</v>
+        <v>129</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4662,13 +4732,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4686,7 +4756,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4701,21 +4771,21 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4726,7 +4796,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4735,19 +4805,19 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>261</v>
-      </c>
       <c r="N29" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4773,13 +4843,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>264</v>
+        <v>77</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4797,16 +4867,16 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -4815,18 +4885,18 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4849,24 +4919,22 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q30" t="s" s="2">
-        <v>270</v>
-      </c>
+      <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
         <v>77</v>
       </c>
@@ -4886,13 +4954,13 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -4910,7 +4978,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4928,29 +4996,29 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -4959,18 +5027,20 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -4995,13 +5065,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5019,7 +5089,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5028,38 +5098,38 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>234</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5068,18 +5138,20 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5128,36 +5200,36 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>234</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>284</v>
+        <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5165,31 +5237,31 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>252</v>
+        <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5197,7 +5269,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>77</v>
@@ -5215,13 +5287,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>159</v>
+        <v>277</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5239,10 +5311,10 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>87</v>
@@ -5254,10 +5326,10 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>77</v>
+        <v>280</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5265,21 +5337,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5288,19 +5360,19 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5326,13 +5398,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>77</v>
+        <v>288</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>77</v>
+        <v>289</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5350,36 +5422,36 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5390,7 +5462,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5399,19 +5471,19 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5437,13 +5509,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>77</v>
+        <v>296</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>77</v>
+        <v>297</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5461,36 +5533,36 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>302</v>
+        <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5501,7 +5573,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5510,23 +5582,27 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>304</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q36" s="2"/>
+      <c r="Q36" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="R36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5546,13 +5622,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>77</v>
+        <v>305</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5570,7 +5646,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5585,10 +5661,10 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5596,10 +5672,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5610,7 +5686,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5622,15 +5698,17 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5655,13 +5733,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5679,31 +5757,31 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>308</v>
+        <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>313</v>
       </c>
@@ -5712,34 +5790,36 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5794,30 +5874,30 @@
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>234</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5828,7 +5908,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -5840,15 +5920,17 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>101</v>
+        <v>284</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>102</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5873,13 +5955,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>77</v>
+        <v>324</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -5897,7 +5979,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>104</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5906,38 +5988,38 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>77</v>
+        <v>326</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>105</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -5949,16 +6031,16 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>108</v>
+        <v>263</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>109</v>
+        <v>328</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>110</v>
+        <v>329</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>111</v>
+        <v>330</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5996,19 +6078,19 @@
         <v>77</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>115</v>
+        <v>327</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6017,27 +6099,27 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>116</v>
+        <v>234</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>77</v>
+        <v>326</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>105</v>
+        <v>236</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6048,7 +6130,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6060,16 +6142,16 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>332</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6119,7 +6201,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6128,27 +6210,27 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM41" t="s" s="2">
-        <v>192</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6162,25 +6244,25 @@
         <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>129</v>
+        <v>338</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6206,13 +6288,13 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>331</v>
+        <v>77</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>332</v>
+        <v>77</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6230,7 +6312,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6245,21 +6327,21 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6267,7 +6349,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>87</v>
@@ -6279,19 +6361,19 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6341,7 +6423,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6356,21 +6438,21 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>77</v>
+        <v>347</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>340</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6378,31 +6460,31 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>101</v>
+        <v>349</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6452,36 +6534,36 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>234</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>77</v>
+        <v>353</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>354</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>192</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6504,13 +6586,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>347</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>348</v>
+        <v>102</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
+        <v>103</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6561,7 +6643,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>104</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6573,35 +6655,35 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6613,15 +6695,17 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6658,31 +6742,31 @@
         <v>77</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6696,21 +6780,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6719,19 +6803,19 @@
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>109</v>
+        <v>358</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>111</v>
+        <v>359</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6769,31 +6853,31 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>115</v>
+        <v>241</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -6802,15 +6886,15 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>105</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6833,16 +6917,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>322</v>
+        <v>244</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>323</v>
+        <v>245</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>324</v>
+        <v>246</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6868,13 +6952,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -6892,7 +6976,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>325</v>
+        <v>249</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6901,7 +6985,7 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>326</v>
+        <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
@@ -6913,15 +6997,15 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6929,13 +7013,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>77</v>
@@ -6944,16 +7028,16 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>129</v>
+        <v>362</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>328</v>
+        <v>251</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>329</v>
+        <v>252</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>330</v>
+        <v>253</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6979,13 +7063,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>331</v>
+        <v>77</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>332</v>
+        <v>77</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7003,7 +7087,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>333</v>
+        <v>254</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7012,7 +7096,7 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>99</v>
@@ -7024,15 +7108,15 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>192</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7040,13 +7124,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>77</v>
@@ -7055,16 +7139,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>355</v>
+        <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>337</v>
+        <v>258</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>338</v>
+        <v>259</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7114,7 +7198,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>339</v>
+        <v>260</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7135,15 +7219,15 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>340</v>
+        <v>194</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7157,25 +7241,25 @@
         <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>101</v>
+        <v>365</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7225,7 +7309,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7234,27 +7318,27 @@
         <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>234</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>77</v>
+        <v>353</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>77</v>
+        <v>354</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>192</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7265,7 +7349,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7274,20 +7358,18 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7312,13 +7394,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7336,40 +7418,40 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>357</v>
+        <v>104</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>363</v>
+        <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>365</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7385,18 +7467,20 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>367</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>368</v>
+        <v>109</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7433,19 +7517,19 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>366</v>
+        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7457,24 +7541,24 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
         <v>371</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7488,24 +7572,26 @@
         <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J54" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K54" t="s" s="2">
-        <v>373</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7554,16 +7640,16 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>372</v>
+        <v>241</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>99</v>
@@ -7575,15 +7661,15 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7603,18 +7689,20 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7639,13 +7727,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7663,7 +7751,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>104</v>
+        <v>249</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7675,7 +7763,7 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
@@ -7684,47 +7772,47 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>105</v>
+        <v>194</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>108</v>
+        <v>374</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>109</v>
+        <v>251</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>111</v>
+        <v>253</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7774,19 +7862,19 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>115</v>
+        <v>254</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
@@ -7795,51 +7883,49 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>105</v>
+        <v>255</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>379</v>
+        <v>77</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>380</v>
+        <v>257</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>381</v>
+        <v>258</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
@@ -7887,19 +7973,19 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>382</v>
+        <v>260</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
@@ -7908,15 +7994,15 @@
         <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7924,10 +8010,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -7936,18 +8022,20 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>101</v>
+        <v>284</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -7972,13 +8060,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -7996,36 +8084,36 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>77</v>
+        <v>382</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8036,7 +8124,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8045,18 +8133,20 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N59" s="2"/>
+      <c r="N59" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8105,7 +8195,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8114,23 +8204,687 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ59" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK59" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>77</v>
+      <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>411</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM59">
+  <autoFilter ref="A1:AM65">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8140,7 +8894,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI58">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
